--- a/AAII_Financials/Quarterly/PKG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PKG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
   <si>
     <t>PKG</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2489900</v>
+      </c>
+      <c r="E8" s="3">
         <v>2367800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2363600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2313400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2171300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2141000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2146100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2182400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2075300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1979500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1937900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1936000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1952100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1976300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1978400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2125900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2237300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2136400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2043200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2000100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1879900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1807200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1714200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1693700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1541600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1708700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1720000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1750700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1759900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1733700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1746500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1809900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1767500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1690600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1684300</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1640100</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1584000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1536500</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>1476600</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>1484000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1972400</v>
+      </c>
+      <c r="E9" s="3">
         <v>1863900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1869100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1790000</v>
       </c>
-      <c r="G9" s="3">
-        <v>1688300</v>
-      </c>
       <c r="H9" s="3">
+        <v>1687300</v>
+      </c>
+      <c r="I9" s="3">
         <v>1682300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1675400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1677200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1637500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1607100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1524800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1520300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1504400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1538900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1528100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1607500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1648500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1603200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1533300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1489400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1431100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1403500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1380900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1348300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1209700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1342900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1336700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1339300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1332000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1312300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1321100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1366700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1346900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1334500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1312600</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1242800</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1219400</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1198000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1149500</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1154500</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>517500</v>
+      </c>
+      <c r="E10" s="3">
         <v>503900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>494500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>523400</v>
       </c>
-      <c r="G10" s="3">
-        <v>483000</v>
-      </c>
       <c r="H10" s="3">
+        <v>484000</v>
+      </c>
+      <c r="I10" s="3">
         <v>458700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>470700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>505200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>437800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>372400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>413100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>415700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>447700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>437400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>450300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>518400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>588800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>533200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>509900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>510700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>448800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>403700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>333300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>345400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>331900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>365800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>383300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>411400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>427900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>421400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>425400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>443200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>420600</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>356100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>371700</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>397300</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>364600</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>338500</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>327100</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>329500</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,175 +1496,181 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>34400</v>
+      </c>
+      <c r="E14" s="3">
         <v>66000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>152000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>38300</v>
       </c>
-      <c r="G14" s="3">
-        <v>-13100</v>
-      </c>
       <c r="H14" s="3">
-        <v>14500</v>
+        <v>-12200</v>
       </c>
       <c r="I14" s="3">
         <v>14500</v>
       </c>
       <c r="J14" s="3">
+        <v>14500</v>
+      </c>
+      <c r="K14" s="3">
         <v>11700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>7500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>17600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>13700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>11900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>13800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>17000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>58000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>4400</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-3100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>2600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>2500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>2900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>74600</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>1200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>300</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>400</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>3400</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>5800</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>7200</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>800</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>-19000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>21500</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>-2000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>3500</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>6000</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>170800</v>
+      </c>
+      <c r="E15" s="3">
         <v>174600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>173800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>152600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>140100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>134900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>133000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>132500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>128500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>126900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>124500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>126800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>124900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>123200</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1723,8 +1746,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2163200</v>
+      </c>
+      <c r="E17" s="3">
         <v>2049400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2043200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1950600</v>
       </c>
-      <c r="G17" s="3">
-        <v>1850700</v>
-      </c>
       <c r="H17" s="3">
+        <v>1849800</v>
+      </c>
+      <c r="I17" s="3">
         <v>1846200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1828300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1842400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1790700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1764800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1664600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1667300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1655900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1690600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1690400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1765600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1821500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1779900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1745900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1647800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1585300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1568900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1525000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1484200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1425500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1499600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1484900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1487900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1479500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1458300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1459800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1511400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1497900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1477700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1432300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1397800</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1350200</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1333400</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1283700</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>1277600</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>326700</v>
+      </c>
+      <c r="E18" s="3">
         <v>318400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>320400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>362800</v>
       </c>
-      <c r="G18" s="3">
-        <v>320600</v>
-      </c>
       <c r="H18" s="3">
+        <v>321500</v>
+      </c>
+      <c r="I18" s="3">
         <v>294800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>317800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>340000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>284600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>214700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>273300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>268700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>296200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>285700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>288000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>360300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>415800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>356500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>297300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>352300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>294600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>238300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>189200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>209500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>116100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>209100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>235100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>262800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>280400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>275400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>286700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>298500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>269600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>212900</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>252000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>242300</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>233800</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>203100</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>192900</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>206400</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,8 +2085,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2096,8 +2130,8 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
-        <v>3600</v>
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R20" s="3">
         <v>3600</v>
@@ -2109,19 +2143,19 @@
         <v>3600</v>
       </c>
       <c r="U20" s="3">
+        <v>3600</v>
+      </c>
+      <c r="V20" s="3">
         <v>4900</v>
-      </c>
-      <c r="V20" s="3">
-        <v>5000</v>
       </c>
       <c r="W20" s="3">
         <v>5000</v>
       </c>
       <c r="X20" s="3">
+        <v>5000</v>
+      </c>
+      <c r="Y20" s="3">
         <v>4800</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>600</v>
       </c>
       <c r="Z20" s="3">
         <v>600</v>
@@ -2133,19 +2167,19 @@
         <v>600</v>
       </c>
       <c r="AC20" s="3">
+        <v>600</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-3100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-3200</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>-3300</v>
       </c>
       <c r="AF20" s="3">
         <v>-3300</v>
       </c>
       <c r="AG20" s="3">
-        <v>-1300</v>
+        <v>-3300</v>
       </c>
       <c r="AH20" s="3">
         <v>-1300</v>
@@ -2154,11 +2188,11 @@
         <v>-1300</v>
       </c>
       <c r="AJ20" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AK20" s="3">
         <v>-700</v>
       </c>
-      <c r="AK20" s="3">
-        <v>0</v>
-      </c>
       <c r="AL20" s="3">
         <v>0</v>
       </c>
@@ -2172,498 +2206,513 @@
         <v>0</v>
       </c>
       <c r="AP20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ20" s="3">
         <v>-23400</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>497500</v>
+      </c>
+      <c r="E21" s="3">
         <v>493000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>494200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>515400</v>
       </c>
-      <c r="G21" s="3">
-        <v>460700</v>
-      </c>
       <c r="H21" s="3">
+        <v>461600</v>
+      </c>
+      <c r="I21" s="3">
         <v>429700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>450800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>472500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>413100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>341600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>397800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>395500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>421100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>408900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>410400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>477900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>533700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>469800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>408600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>462900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>404300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>343900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>290700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>310600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>224900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>310000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>330900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>357500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>373000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>366900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>382700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>398600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>372400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>320300</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>359700</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>339800</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>327500</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>295600</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>286600</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>271000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>33300</v>
+      </c>
+      <c r="E22" s="3">
         <v>32600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>29000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>19300</v>
       </c>
-      <c r="G22" s="3">
-        <v>13000</v>
-      </c>
       <c r="H22" s="3">
+        <v>13100</v>
+      </c>
+      <c r="I22" s="3">
         <v>12900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>9900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>9700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>10400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>9600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>9500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>12300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>14600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>15400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>15100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>16500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>18800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>19800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>21800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>23400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>24900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>23500</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>24400</v>
       </c>
       <c r="Z22" s="3">
         <v>24400</v>
       </c>
       <c r="AA22" s="3">
+        <v>24400</v>
+      </c>
+      <c r="AB22" s="3">
         <v>25100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>19600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>59600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>20300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>21100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>22800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>20900</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>23100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>23000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>25600</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>28000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>25400</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>25200</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>24000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>24300</v>
       </c>
-      <c r="AP22" s="3" t="s">
+      <c r="AQ22" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>259000</v>
+      </c>
+      <c r="E23" s="3">
         <v>219800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>134500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>305200</v>
       </c>
-      <c r="G23" s="3">
-        <v>320700</v>
-      </c>
       <c r="H23" s="3">
+        <v>320600</v>
+      </c>
+      <c r="I23" s="3">
         <v>267400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>291600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>318600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>266700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>187500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>248500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>244500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>267800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>253300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>276500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>347400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>400600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>340300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>280400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>333900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>274700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>219600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>165400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>185700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>91600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>190100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>172400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>239300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>256000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>249300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>264500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>274100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>245300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>186600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>224000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>216900</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>208600</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>179100</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>168600</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>183000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>66900</v>
+      </c>
+      <c r="E24" s="3">
         <v>48900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>32700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>78300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>79100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>63600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>70500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>80500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>67700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>40600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>59300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>61300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>65100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>63200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>64900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>84900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>99100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>86100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>63900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>83200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>67400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>53100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>41800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>46600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>34900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>48400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>36200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>59500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>62400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>62500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>61900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>67400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>58700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>46500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>77200</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>77800</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>65400</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>61700</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>57900</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>63700</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>192100</v>
+      </c>
+      <c r="E26" s="3">
         <v>170900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>101800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>226900</v>
       </c>
-      <c r="G26" s="3">
-        <v>241600</v>
-      </c>
       <c r="H26" s="3">
+        <v>241500</v>
+      </c>
+      <c r="I26" s="3">
         <v>203800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>221100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>238100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>199000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>146900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>189200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>183200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>202700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>190100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>211600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>262500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>301500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>254200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>216500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>250700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>207300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>166500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>123600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>139100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>56700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>141700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>136200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>179800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>193600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>186800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>202600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>206700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>186600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>140100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>146800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>139100</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>143200</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>117400</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>110700</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>119300</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>191000</v>
+      </c>
+      <c r="E27" s="3">
         <v>169800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>92100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>228400</v>
       </c>
-      <c r="G27" s="3">
-        <v>246000</v>
-      </c>
       <c r="H27" s="3">
+        <v>239900</v>
+      </c>
+      <c r="I27" s="3">
         <v>202400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>211400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>239800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>202400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>145900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>187800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>181800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>200800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>188500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>210100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>260600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>298900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>252200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>215000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>249000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>205500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>165200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>122700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>138100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>56200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>140500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>135200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>178500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>192100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>185400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>201000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>205100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>185200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>139000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>144600</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>138000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>142000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>116400</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>109700</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3224,8 +3285,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -3242,24 +3303,24 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>2000</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>122100</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,8 +3583,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3560,8 +3630,8 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
-        <v>-3600</v>
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R32" s="3">
         <v>-3600</v>
@@ -3573,19 +3643,19 @@
         <v>-3600</v>
       </c>
       <c r="U32" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="V32" s="3">
         <v>-4900</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-5000</v>
       </c>
       <c r="W32" s="3">
         <v>-5000</v>
       </c>
       <c r="X32" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-4800</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-600</v>
       </c>
       <c r="Z32" s="3">
         <v>-600</v>
@@ -3597,19 +3667,19 @@
         <v>-600</v>
       </c>
       <c r="AC32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AD32" s="3">
         <v>3100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>3200</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>3300</v>
       </c>
       <c r="AF32" s="3">
         <v>3300</v>
       </c>
       <c r="AG32" s="3">
-        <v>1300</v>
+        <v>3300</v>
       </c>
       <c r="AH32" s="3">
         <v>1300</v>
@@ -3618,11 +3688,11 @@
         <v>1300</v>
       </c>
       <c r="AJ32" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AK32" s="3">
         <v>700</v>
       </c>
-      <c r="AK32" s="3">
-        <v>0</v>
-      </c>
       <c r="AL32" s="3">
         <v>0</v>
       </c>
@@ -3636,132 +3706,138 @@
         <v>0</v>
       </c>
       <c r="AP32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ32" s="3">
         <v>23400</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>192100</v>
+      </c>
+      <c r="E33" s="3">
         <v>170900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>101800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>226900</v>
       </c>
-      <c r="G33" s="3">
-        <v>241600</v>
-      </c>
       <c r="H33" s="3">
+        <v>241500</v>
+      </c>
+      <c r="I33" s="3">
         <v>203800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>221100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>238100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>199000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>146900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>189200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>183200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>202700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>190100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>210100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>260600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>298900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>252200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>215000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>249000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>205500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>165200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>122700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>138100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>56200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>140500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>135200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>178500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>192100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>185400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>203000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>205100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>185200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>139000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>266700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>138000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>142000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>116400</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>109700</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>192100</v>
+      </c>
+      <c r="E35" s="3">
         <v>170900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>101800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>226900</v>
       </c>
-      <c r="G35" s="3">
-        <v>241600</v>
-      </c>
       <c r="H35" s="3">
+        <v>241500</v>
+      </c>
+      <c r="I35" s="3">
         <v>203800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>221100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>238100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>199000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>146900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>189200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>183200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>202700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>190100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>210100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>260600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>298900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>252200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>215000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>249000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>205500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>165200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>122700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>138100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>56200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>140500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>135200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>178500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>192100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>185400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>203000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>205100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>185200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>139000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>266700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>138000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>142000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>116400</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>109700</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,214 +4305,218 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>442800</v>
+      </c>
+      <c r="E41" s="3">
         <v>397100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>529000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>634000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>787900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>751700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>685000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>676600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>613600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>692400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>648000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>573200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>477100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>367700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>320000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>648700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>667300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>628600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>618700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1702900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>972200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>983400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>974600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>949100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>853300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>764000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>679500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>738300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>569400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>442400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>361500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>293800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>199600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>102400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>216900</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>370500</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>321000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>254000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>239300</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>279800</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>151000</v>
+      </c>
+      <c r="E42" s="3">
         <v>146600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>71800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>94700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>92400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>91400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>102000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>95000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>490800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>492300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>493500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>104000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>101900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>95600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>85200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>77700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>82300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>81300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>86100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>88300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>101700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>102500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>105600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>101200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>86900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>92300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>87900</v>
       </c>
-      <c r="AD42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE42" s="3" t="s">
         <v>8</v>
       </c>
@@ -4439,8 +4529,8 @@
       <c r="AH42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI42" s="3">
-        <v>0</v>
+      <c r="AI42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ42" s="3">
         <v>0</v>
@@ -4463,252 +4553,261 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1463100</v>
+      </c>
+      <c r="E43" s="3">
         <v>1351100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1283900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1410500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1205900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1164100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1154200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1216100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1145500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1045100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1037500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1045200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1023900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1031400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1067500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1118900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1212000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1140700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1078400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1078100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>981400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>908600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>837500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>864600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>823400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>879500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>872100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>941800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>958400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>930300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>918600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>991300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>936700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>908800</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>900200</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>851300</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>755200</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>733300</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>703100</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>731500</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1262400</v>
+      </c>
+      <c r="E44" s="3">
         <v>1258400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1243200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1277100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1144700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1140600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1124900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1061900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1029500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1003600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1013100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>986100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>992200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1003400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>977300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>994900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>954200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>941200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>902500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>880100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>827200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>799600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>787900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>777600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>834500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>809900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>794100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>806300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>815700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>831700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>795600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>780600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>763700</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>766400</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>762500</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>736600</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>734400</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>744500</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>723600</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>690600</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4730,15 +4829,15 @@
       <c r="I45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
         <v>127700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>125700</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4751,292 +4850,298 @@
       <c r="P45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R45" s="3">
         <v>58300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>67300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>74600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>77600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>47000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>55400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>78600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>62800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>44700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>51200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>60900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>67900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>44800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>44900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>59200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>58000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>39400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>49000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>56600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>55000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>35500</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>43400</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>52800</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>47300</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>30300</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>45100</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3423600</v>
+      </c>
+      <c r="E46" s="3">
         <v>3257600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3213700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3497400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3336600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3302500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3233000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3241400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3483900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3445100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3254400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2773300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2670600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2585400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2508300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2907500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2990400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2869400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2732700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3804800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2961100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2856900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2750300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2743700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2659000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2613600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2478400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2531300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2402700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2262400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2115100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2114700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1956600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1832600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>1915100</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>2001800</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>1863400</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>1779100</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>1696300</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>1747000</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>73000</v>
+      </c>
+      <c r="E47" s="3">
         <v>71800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>67000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>77700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>75600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>71300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>65200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>69700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>68400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>68500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>64100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>49300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>50600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>56900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>64900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>67100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>61200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>68500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>60000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>57800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>49900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>47000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>42700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>45200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>36300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>57100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>58100</v>
       </c>
-      <c r="AD47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE47" s="3" t="s">
         <v>8</v>
       </c>
@@ -5049,8 +5154,8 @@
       <c r="AH47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI47" s="3">
-        <v>0</v>
+      <c r="AI47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ47" s="3">
         <v>0</v>
@@ -5073,252 +5178,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5424900</v>
+      </c>
+      <c r="E48" s="3">
         <v>5373100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5361100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5412300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4430300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4386400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4315900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4242600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4228300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4133900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4143400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4142400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4172900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4185200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4198300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4100000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4036700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3935100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3767300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3591200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3473500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3444000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3427600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3362600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3344400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3373900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3386000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3342700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3345200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3327100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3108600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>3065100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>3026500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>2961400</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>2924900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>2881600</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>2872500</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>2887200</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>2895700</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>2878700</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1981900</v>
+      </c>
+      <c r="E49" s="3">
         <v>1965600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1975200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1890400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1095500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1104900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1115300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1123700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1133100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1142500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1153900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1161600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1171100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1180700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1190300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1199800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1209800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1221300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1231900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1131200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1140500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1149800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1159400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1168900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1178400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1247900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1257500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1267200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1276900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1286000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1295500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1262600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1272800</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1282800</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1293200</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1079900</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>1087300</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>1095900</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>1105000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>1046900</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>112100</v>
+      </c>
+      <c r="E52" s="3">
         <v>109800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>87000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>102200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>103200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>104700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>80700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>76400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>68400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>67000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>42600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>51000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>41300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>40800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>42000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>70000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>42500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>43500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>44900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>45800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>48600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>51300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>53200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>52200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>53900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>55100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>55800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>49900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>49600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>53100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>50500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>57600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>59700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>63000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>64300</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>63900</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>80000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>81200</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>80000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>74600</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11015500</v>
+      </c>
+      <c r="E54" s="3">
         <v>10777900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10725500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10980000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9041200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8969800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8833200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8753800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8982100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8857000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8681100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8177600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8106500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8049000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8003800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8344400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>8340600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>8137800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7836800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>8630800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7673600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7549000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7433200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7372600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7272000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>7347600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>7235800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>7191100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>7074400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>6928600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>6569700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>6500000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>6315600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>6139800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>6197500</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>6027200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>5903200</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>5843400</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>5777000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>5747200</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,177 +6145,181 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>616900</v>
+      </c>
+      <c r="E57" s="3">
         <v>557000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>471400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>554200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>490700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>480900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>430300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>459900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>474500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>449600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>402400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>405900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>365800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>410500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>410400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>485300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>528200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>546700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>452400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>499100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>405300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>402500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>387000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>352100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>315200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>389000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>351900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>385500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>382800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>405100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>382200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>438900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>431700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>427300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>402900</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>379500</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>349200</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>367300</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>323800</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>106800</v>
+      </c>
+      <c r="E58" s="3">
         <v>104400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>102100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>98200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>88900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>86300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>82600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>83800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>482300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>481000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>480200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>478600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>76900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>74600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1900</v>
-      </c>
-      <c r="R58" s="3">
-        <v>1800</v>
       </c>
       <c r="S58" s="3">
         <v>1800</v>
@@ -6194,19 +6328,19 @@
         <v>1800</v>
       </c>
       <c r="U58" s="3">
+        <v>1800</v>
+      </c>
+      <c r="V58" s="3">
         <v>1700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>699800</v>
-      </c>
-      <c r="W58" s="3">
-        <v>1700</v>
       </c>
       <c r="X58" s="3">
         <v>1700</v>
       </c>
       <c r="Y58" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="Z58" s="3">
         <v>1600</v>
@@ -6218,7 +6352,7 @@
         <v>1600</v>
       </c>
       <c r="AC58" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="AD58" s="3">
         <v>1500</v>
@@ -6230,7 +6364,7 @@
         <v>1500</v>
       </c>
       <c r="AG58" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="AH58" s="3">
         <v>1400</v>
@@ -6242,10 +6376,10 @@
         <v>1400</v>
       </c>
       <c r="AK58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AL58" s="3">
         <v>151300</v>
-      </c>
-      <c r="AL58" s="3">
-        <v>157800</v>
       </c>
       <c r="AM58" s="3">
         <v>157800</v>
@@ -6254,310 +6388,319 @@
         <v>157800</v>
       </c>
       <c r="AO58" s="3">
+        <v>157800</v>
+      </c>
+      <c r="AP58" s="3">
         <v>27100</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>27000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>136900</v>
+      </c>
+      <c r="E59" s="3">
         <v>113100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>120600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>120700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>115800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>204700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>212500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>258700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>241100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>256100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>115900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>123800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>123400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>133600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>463200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>476300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>442900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>419400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>430700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>445500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>409800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>401600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>394000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>421700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>366800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>354000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>370400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>383700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>345300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>334100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>310000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>326200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>282700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>244900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>278500</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>287000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>253200</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>250900</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>274500</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>283500</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1163900</v>
+      </c>
+      <c r="E60" s="3">
         <v>1060900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1015100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1107500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>943000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1007700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1001600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1100500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1431500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1400300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1265700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1278900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>797700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>828900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>875500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>963400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>972900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>967900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>884800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1644400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>816800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>805800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>782600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>775400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>683600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>744600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>723800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>770700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>729600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>740700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>693600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>766500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>715800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>673600</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>832700</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>824300</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>760200</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>776000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>625400</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>637500</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4297500</v>
+      </c>
+      <c r="E61" s="3">
         <v>4262500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4262800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4258700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2721900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2716200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2688900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2670300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2678000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2681700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2693000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2298000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2706400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2709500</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>2484400</v>
       </c>
       <c r="R61" s="3">
         <v>2484400</v>
       </c>
       <c r="S61" s="3">
+        <v>2484400</v>
+      </c>
+      <c r="T61" s="3">
         <v>2484300</v>
-      </c>
-      <c r="T61" s="3">
-        <v>2484200</v>
       </c>
       <c r="U61" s="3">
         <v>2484200</v>
@@ -6566,189 +6709,195 @@
         <v>2484200</v>
       </c>
       <c r="W61" s="3">
+        <v>2484200</v>
+      </c>
+      <c r="X61" s="3">
         <v>2493300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2494000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2493800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2493500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2493200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2493000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2492800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2502700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2502200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2501800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2501300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2500800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2500400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2499800</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2499400</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2475600</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>2477000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>2478400</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>2640300</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>2646500</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>210900</v>
+      </c>
+      <c r="E62" s="3">
         <v>189100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>130600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>186500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>179300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>175900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>121300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>178900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>193900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>177500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>91800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>176700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>215200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>206700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>976800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>925400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>918900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>906400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>860600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>893900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>919200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>918000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>910500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>898300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>962100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>960100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>948200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>883000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>921400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>891500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>702400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>702500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>711400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>692600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>682800</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>733100</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>759400</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>764300</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>751500</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>733200</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6353600</v>
+      </c>
+      <c r="E66" s="3">
         <v>6190100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6127500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6224500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4409100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4470600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4429200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4490200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4855500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4826000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4683800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4290400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4257900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4291300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4336700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4373200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4376100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4358500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4229600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5022500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4229300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4217800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4186900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4167200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4138900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4197700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4164800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4156400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4153200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>4134000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3897300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3969800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>3927600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>3866000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>4014900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>4033000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>3996600</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>4018700</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>4017200</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>4017600</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3962700</v>
+      </c>
+      <c r="E72" s="3">
         <v>3906400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3931000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>4087300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3973500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3852800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3776700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3669100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3544400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3459600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3447200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3370500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3339000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3259300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3186800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3443500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>3437000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3261900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3102100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3162800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>3008500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2906300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2835500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2806700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2742900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2771100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2704800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2643700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2539200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2427800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2315800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>2185500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>2054000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>1949600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>1867400</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>1658200</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>1578800</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>1504500</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>1447100</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>1396900</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4661900</v>
+      </c>
+      <c r="E76" s="3">
         <v>4587800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4598000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4755500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4632100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4499200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4404000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4263600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4126600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4031000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3997300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3887200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3848600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3757700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3667100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3971200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3964500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3779300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3607200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3608300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3444300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3331200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3246300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3205400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3133100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3149900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3071000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3034700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2921200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2794600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2672400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>2530200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>2388000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>2273800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>2182600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>1994200</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>1906600</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>1824700</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>1759800</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>1729600</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>192100</v>
+      </c>
+      <c r="E81" s="3">
         <v>170900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>101800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>226900</v>
       </c>
-      <c r="G81" s="3">
-        <v>241600</v>
-      </c>
       <c r="H81" s="3">
+        <v>241500</v>
+      </c>
+      <c r="I81" s="3">
         <v>203800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>221100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>238100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>199000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>146900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>189200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>183200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>202700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>190100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>210100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>260600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>298900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>252200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>215000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>249000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>205500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>165200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>122700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>138100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>56200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>140500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>135200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>178500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>192100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>185400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>203000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>205100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>185200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>139000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>266700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>138000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>142000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>116400</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>109700</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>118200</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>130700</v>
+      </c>
+      <c r="E83" s="3">
         <v>125500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>123600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>123100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>119100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>117400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>114900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>117300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>115300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>113600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>102800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>102700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>104100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>98400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>118800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>114000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>114300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>109700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>106400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>105600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>104700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>100800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>100900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>100500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>108200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>100300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>98900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>97900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>95900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>94800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>97300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>101400</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>104100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>108100</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>107700</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>97500</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>93700</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>92500</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>93700</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>88000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>376000</v>
+      </c>
+      <c r="E89" s="3">
         <v>329300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>446600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>472200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>299600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>339100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>325400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>327100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>278300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>260400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>335300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>339500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>359900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>280400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>420100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>430600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>319000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>325300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>390700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>283600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>228200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>191600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>271100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>298200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>226800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>236700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>329200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>339800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>302400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>236000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>345600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>301000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>331000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>202500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>272800</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>197700</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>221500</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>164100</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>213400</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>217300</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-205900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-164700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-319000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-192100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-169700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-148100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-201300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-146700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-245000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-76700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-141100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-89800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-126400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-112400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-247500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-182800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-184500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-215600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-238900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-149900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-2700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-900</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-60700</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-174400</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-139000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-216600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-260900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-285500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2000400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-142800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-144200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-203300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>249300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-242800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-81000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-544000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-88900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-126800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-115400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-251800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-183800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-176900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-221200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-429400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-144800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-132700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-87500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-170200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-127100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-51800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-77000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-278300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-95500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-92700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-80100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-202900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-131800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-166300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-107200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-381500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-86700</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-83100</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-57800</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-186900</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-455000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,25 +10455,26 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>111300</v>
+      </c>
+      <c r="E96" s="3">
         <v>111900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>112500</v>
-      </c>
-      <c r="F96" s="3">
-        <v>112400</v>
       </c>
       <c r="G96" s="3">
         <v>112400</v>
       </c>
       <c r="H96" s="3">
-        <v>112300</v>
+        <v>112400</v>
       </c>
       <c r="I96" s="3">
         <v>112300</v>
@@ -10249,37 +10483,37 @@
         <v>112300</v>
       </c>
       <c r="K96" s="3">
+        <v>112300</v>
+      </c>
+      <c r="L96" s="3">
         <v>112200</v>
-      </c>
-      <c r="L96" s="3">
-        <v>112000</v>
       </c>
       <c r="M96" s="3">
         <v>112000</v>
       </c>
       <c r="N96" s="3">
-        <v>112400</v>
+        <v>112000</v>
       </c>
       <c r="O96" s="3">
         <v>112400</v>
       </c>
       <c r="P96" s="3">
+        <v>112400</v>
+      </c>
+      <c r="Q96" s="3">
         <v>112100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-115900</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-117200</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-93600</v>
       </c>
       <c r="T96" s="3">
         <v>-93600</v>
       </c>
       <c r="U96" s="3">
-        <v>-95000</v>
+        <v>-93600</v>
       </c>
       <c r="V96" s="3">
         <v>-95000</v>
@@ -10288,43 +10522,43 @@
         <v>-95000</v>
       </c>
       <c r="X96" s="3">
+        <v>-95000</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-94800</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-75000</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-74900</v>
       </c>
       <c r="AA96" s="3">
         <v>-74900</v>
       </c>
       <c r="AB96" s="3">
-        <v>-74800</v>
+        <v>-74900</v>
       </c>
       <c r="AC96" s="3">
         <v>-74800</v>
       </c>
       <c r="AD96" s="3">
-        <v>-74600</v>
+        <v>-74800</v>
       </c>
       <c r="AE96" s="3">
         <v>-74600</v>
       </c>
       <c r="AF96" s="3">
-        <v>-74700</v>
+        <v>-74600</v>
       </c>
       <c r="AG96" s="3">
         <v>-74700</v>
       </c>
       <c r="AH96" s="3">
+        <v>-74700</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-74500</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-59500</v>
-      </c>
-      <c r="AJ96" s="3">
-        <v>-59400</v>
       </c>
       <c r="AK96" s="3">
         <v>-59400</v>
@@ -10342,10 +10576,13 @@
         <v>-59400</v>
       </c>
       <c r="AP96" s="3">
+        <v>-59400</v>
+      </c>
+      <c r="AQ96" s="3">
         <v>-51800</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,97 +10953,100 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-113700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-200300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-266100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1374300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-120600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-128200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-113700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-513400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-114300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-135000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>283500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-154500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-123700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-117300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-497000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-265400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-103400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-94200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1045500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>591900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-106700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-95300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-75400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-75300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-85700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-75200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-109700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-75400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-82700</v>
-      </c>
-      <c r="AF100" s="3">
-        <v>-75000</v>
       </c>
       <c r="AG100" s="3">
         <v>-75000</v>
@@ -10809,31 +11055,34 @@
         <v>-75000</v>
       </c>
       <c r="AI100" s="3">
+        <v>-75000</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>-67500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-209800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-44900</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-61500</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-71400</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-91600</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-66600</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>304100</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10876,8 +11125,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10954,126 +11203,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>45700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-131900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-105000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-153900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>36200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>66700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>8400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>63000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-78800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>44400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>74800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>96100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>109400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>47700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-328700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-18600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>38700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>9900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1084200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>730700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-11200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>8800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>25500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>95800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>89300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>84500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-58800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>168900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>127000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>80900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>67700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>94200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>97200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-114500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-153600</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>49500</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>67000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>14700</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-40500</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>66200</v>
       </c>
     </row>
